--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
@@ -88,21 +88,21 @@
     </font>
     <font>
       <name val="游ゴシック"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -111,7 +111,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -121,11 +121,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -214,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -229,27 +224,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -638,7 +636,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>文書名</t>
@@ -650,7 +648,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
+    <row r="6" ht="17.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>文書番号</t>
@@ -662,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
+    <row r="7" ht="17.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>版</t>
@@ -670,11 +668,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0.10(草案・未検証)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
+          <t>0.11(草案・未検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>対象システム</t>
@@ -686,7 +684,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
+    <row r="9" ht="17.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>作成</t>
@@ -698,7 +696,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10" ht="17.5" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>作成チームリーダー</t>
@@ -710,7 +708,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
+    <row r="11" ht="17.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>承認 / 検印</t>
@@ -722,7 +720,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
+    <row r="12" ht="17.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>作成日 / 承認日</t>
@@ -734,7 +732,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
+    <row r="13" ht="17.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>様式の参考</t>
@@ -746,7 +744,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
+    <row r="14" ht="17.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>文書状態</t>
@@ -758,7 +756,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
+    <row r="15" ht="17.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>認証情報</t>
@@ -784,8 +782,8 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -794,15 +792,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -815,6 +815,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -829,46 +834,49 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8. バックアップ / 8-1 取得の手順</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>周期は毎日とする(2026-09-30 会議の決定)。DGS で取得したものを Pana-CIM で保存する。日次点検の Step 2(第6章)で最終実行日時と成否を確認する。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>出典は 不具合別ログリスト_取得手順_Ｊ.pdf(PDF通し11〜12頁)。原文は付録A-1。</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>手順1</t>
         </is>
@@ -879,8 +887,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>手順2</t>
         </is>
@@ -891,8 +899,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>手順3</t>
         </is>
@@ -903,8 +911,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>手順4</t>
         </is>
@@ -915,8 +923,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>手順5</t>
         </is>
@@ -927,8 +935,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>手順6</t>
         </is>
@@ -939,116 +947,120 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="18"/>
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>保存先の表記について。原文のPDFから抽出した文字列は E\BackUP_DB で、ドライブ文字の後のコロンが落ちている。本書では E:\BackUP_DB と書いた。実機の画面で正しい保存先を確認すること(第14章 No.11)。</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>8-2 確定していないこと</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>ファイル名の正式な命名規則</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>要確認。原文の ****.**.** は抽出時の伏字</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>外部媒体の種類と管理</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>保持する世代数と期間</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>取得者と取得時刻</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="70.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="28" ht="31" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>成否を確認する担当者</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>要確認。本節で最も重要。現状: L1/L2/L3 それぞれで取得していることは会議で確認済みだが、誰が・いつ・どこに保存しているかは未確認。確認先の候補挙げは篠原が実施し(会議記録 §10 持ち帰りタスク)、実施者の確定は本会議(10-14)で判断する</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="29"/>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>バックアップ障害は「成否を確認する担当が決まっていなかった」ことで長期化している。Eg-Pro のサブサーバー同期は1年以上、nksv523 は6月から暫定運用のまま。手順書を作るだけでは同じことが起きる。誰がどこで結果を確認し、失敗時に何をするかまで決める。</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1059,6 +1071,9 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1073,8 +1088,8 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1083,15 +1098,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1104,6 +1121,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1118,20 +1140,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>9. 復旧</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
@@ -1142,8 +1165,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>実施条件</t>
         </is>
@@ -1154,8 +1177,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
@@ -1166,8 +1189,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>確認の頻度</t>
         </is>
@@ -1178,8 +1201,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>記録様式</t>
         </is>
@@ -1190,24 +1213,28 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>戻す試験を一度もしていない。本書の初版では復旧手順を確定できていない。</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1222,9 +1249,9 @@
   <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -1232,15 +1259,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1253,6 +1282,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1267,20 +1301,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>10. 異常時の対応 / 10-1 アンドンの色定義</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
@@ -1291,8 +1326,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="44.5" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>記載する事象</t>
         </is>
@@ -1303,8 +1338,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="44.5" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>稼働モニタ</t>
         </is>
@@ -1315,8 +1350,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>色定義の表</t>
         </is>
@@ -1327,21 +1362,23 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>10-2 中断と連絡</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="16" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="31" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -1352,8 +1389,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>最初の連絡先</t>
         </is>
@@ -1364,8 +1401,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>連絡がつかない場合</t>
         </is>
@@ -1376,8 +1413,8 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="31" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>その場で行ってよい対応</t>
         </is>
@@ -1388,8 +1425,8 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>行ってはいけない対応</t>
         </is>
@@ -1400,8 +1437,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>中断して連絡する条件</t>
         </is>
@@ -1412,34 +1449,37 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>バックアップ失敗、保存領域不足、通信異常は記録番号を付して申し送る。復旧操作とサーバ構成の変更は本手順の範囲外。ベンダーへの依頼境界は要確認。</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="n"/>
-    </row>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>10-3 不具合の記録</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="31" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>媒体</t>
         </is>
@@ -1450,8 +1490,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="31" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>事例</t>
         </is>
@@ -1462,8 +1502,8 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="28" ht="31" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
@@ -1474,47 +1514,51 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>10-4 異常時のサーバー再起動</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="n"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="16" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>本手順は全ラインの生産と作業を停止させる。第7章の月次再起動とはまったく別の手順である。実施には停止判断者の承認が要る。</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="n"/>
-    </row>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="16" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>発動条件(原文): 生産時、「生産情報が取得できません。」とエラーが発生し情報の取得ができない場合、以下の手順で PanaCIM サーバーの再起動を実施してください。</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="16" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
@@ -1525,8 +1569,8 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="37" ht="44.5" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>構成</t>
         </is>
@@ -1537,509 +1581,518 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>原文との突合(完全性立証 / 2026-10-13 実施)</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="17.5" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>原文の位置</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>突合結果</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="42" ht="17.5" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>発動条件</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>「PanaCIM」シート 行6-7</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>一致(「生産情報が取得できません。」)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>手順1〜14</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>行9〜277(14手順+注記6件)</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>全14手順の文言が一致。逸脱なし</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>手順2/8 のパスワード</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>行12/149 に平文記載</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>本書では伏字とし保管先参照に変更(意図的な差分。セキュリティ方針による)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="45" ht="17.5" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>手順6 の表記</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>行114「windwos」</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>綴りを訂正し「Windows」と記載(意図的な差分。注記あり)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>手順の構成</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>停止・起動が連続記載</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>第1段(停止)/第2段(起動)に分けて構造化(意図的な差分。中断の危険を明示するため)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="47" ht="17.5" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>「PanaCIM」シートに画像なし(2026-10-13 確認)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>本書の image/ 14枚は本xlsxに依存しない別ソース。対応付けは要確認No.23のまま</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="48"/>
+    <row r="49" ht="17.5" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>結論: 手順内容は原文から変化していない。差分は3点(パスワード伏字/綴り訂正/2段構成)で、いずれも意図的かつ注記済みである。</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="14" t="n"/>
-    </row>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="16" t="n"/>
+    </row>
+    <row r="50"/>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>第1段 停止(手順1〜6)</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="14" t="n"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="16" t="n"/>
+    </row>
+    <row r="52"/>
+    <row r="53" ht="17.5" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="54" ht="17.5" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>全ラインの生産と作業を停止させる</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>ここから先は生産が止まる</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="55" ht="31" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>「CIM-C」画面に移動し、①→②→③の順に選択する。シャットダウン時にパスワードを要求される</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>①②③は画面上の番号。画像を参照する(要対応付け)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="56" ht="31" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>停止後、ペンギンの写真が出てくる。出てきたら「CIM-C」の画面を閉じる</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>image/画像2.png がこの画面。赤丸がペンギンと閉じるボタン</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="57" ht="17.5" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>ホスト → アクション → メンテナンスモードを選択する</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>「メンテナンスモードへ変更しますか?」に「はい」</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="58" ht="17.5" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>①→②の順で選択する。初期画面が表示されたら×で閉じる</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>①②は画面上の番号。画像を参照する(要対応付け)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="59" ht="31" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>CIM-A PC は Windows ボタンを選択後、シャットダウンを選択する</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>原文は windwos。綴りの誤りと判断し、本書では Windows と記した</t>
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>第2段 起動(手順7〜14)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="14" t="n"/>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="16" t="n"/>
+    </row>
+    <row r="62"/>
+    <row r="63" ht="17.5" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="16.5" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="64" ht="17.5" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>CIM-C PC と CIM-A PC の電源を立ち上げる</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>電源投入後は約3分待つ</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="65" ht="17.5" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>モニターに CIM-A PC の情報が表示されるのでログオンする</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>サーバーマネージャーが起動しているので閉じる</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="66" ht="31" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Firefox アイコンをクリックし、VMware アイコンをクリックする</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67" ht="17.5" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>ユーザー名、パスワードを入力し、ログオンボタンを選択する</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>どのアカウントかは要確認</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="68" ht="17.5" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>ホスト → アクション → メンテナンスモードの終了を選択する</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>ここを飛ばすと手順12で仮想マシンを起動できない</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="69" ht="17.5" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>CIMC-SV → アクション → パワーオンを選択する</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+    </row>
+    <row r="70" ht="31" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>画像部分をクリックして拡大し、ユーザーとパスワードを入力する</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>立上げ途中に画面が出た場合は「Continue」をクリックする</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="71" ht="17.5" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>画面が起動するので「Route Editer」を選択して立上げ完了</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>原文の表記のまま(2026-10-13 原文シートで表記を確認済み)。画面の表示と一致するか要確認</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="A73" s="18" t="inlineStr">
+    <row r="72"/>
+    <row r="73" ht="17.5" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>パスワードは本書に書かない。手順2、8、10、13 で必要になる値は、承認済みの保管先を参照する(第12章)。</t>
         </is>
       </c>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="13" t="n"/>
-      <c r="D73" s="13" t="n"/>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
-      <c r="G73" s="14" t="n"/>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="15" t="n"/>
+      <c r="G73" s="16" t="n"/>
+    </row>
+    <row r="74"/>
+    <row r="75" ht="17.5" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="76" ht="17.5" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>所要時間</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>要確認(手順7の3分以外は記載がない)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
+    <row r="77" ht="17.5" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>実施の判断者</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="78" ht="17.5" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="43.5" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="79" ht="44.5" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>画像と手順の対応付け</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>image/ に14枚ある。手順3は 画像2.png と確認済み。残りは要対応付け。既存xlsxの埋込み画像136個とはMD5不一致のため、対応付けは継続課題</t>
         </is>
@@ -2060,6 +2113,9 @@
     <mergeCell ref="A73:G73"/>
     <mergeCell ref="A49:G49"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2074,8 +2130,8 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -2084,15 +2140,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2105,6 +2163,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2119,170 +2182,173 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>11. 記録の管理</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>保存先</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>保存期間</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>確認者と確認の時期</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>画面やコマンド出力の保存先</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>12. 変更と文書管理</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>文書番号の付番規則</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>文書の保管場所</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>改訂の承認者</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>改訂の見直し時期</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>暫定版を作成し運用しながら改訂する方針は確定。時期と頻度は未確定</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>様式の拡張</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>操作の種別・取り消し可否・中断条件の3欄を ZZZ-90000 に追加できるかが未確認</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>認証情報の保管先</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>要確認。本書が参照する「承認済みの保管先」を確定させる</t>
         </is>
@@ -2293,6 +2359,9 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2307,25 +2376,27 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2338,6 +2409,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2352,20 +2428,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>13-1 日次チェックシート</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>対象システム</t>
         </is>
@@ -2376,8 +2453,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>年月</t>
         </is>
@@ -2388,8 +2465,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
@@ -2400,110 +2477,114 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>空欄のまま提出しない。実施しなかった項目は「未実施」または「該当なし」と書く。空欄は「実施したが記入を忘れた」と区別できない。状態を変える操作は、同席者と権限者の判断を記録する。</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>稼働モニタ/アンドン</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>バックアップ日時・成否</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>空き容量</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>異常記録No.</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>記入方法</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="85" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>稼働状態</t>
         </is>
@@ -2514,8 +2595,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="125.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>バックアップ結果</t>
         </is>
@@ -2526,8 +2607,8 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>保存領域</t>
         </is>
@@ -2538,8 +2619,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="44.5" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
@@ -2556,6 +2637,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A12:G12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2570,25 +2654,27 @@
   <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2601,6 +2687,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2615,533 +2706,544 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>13-2 バックアップ記録</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>保存先</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>成功表示</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>ファイル名</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>媒体退避・圧縮</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-    </row>
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>13-3 月次再起動チェックシート(第7章)</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>SMT点検日であることを確認した</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Pana-CIM が動いていないことを確認した</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>対象が CIMC-SV であることを確認した</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>スタート→再起動を実施した</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>理由コード「その他(計画外)」を選択した</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="71.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>再起動後に稼働モニタとアンドンの表示を確認した</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-    </row>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>随時再起動の記入欄を設けるかは未確定のため、本様式には設けていない。</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="n"/>
-    </row>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>13-4 異常時の再起動チェックシート(第10章10-4)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>全ラインを停止させる手順。実施前に停止判断者の承認を記録する。</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>段</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>実施時刻</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="44.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>前</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>発動条件(「生産情報が取得できません。」)を確認した</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>前</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>停止判断者の承認を得た</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31" ht="31" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>1 全ラインの生産と作業を停止させた</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="44.5" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2〜3 CIM-C をシャットダウンし、ペンギン表示を確認して閉じた</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33" ht="31" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>4 メンテナンスモードへ変更した</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>6 CIM-A PC をシャットダウンした</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>起動</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>7 両PCの電源を入れ、3分待った</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>起動</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>11 メンテナンスモードを終了した</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="31" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>起動</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>12 CIMC-SV をパワーオンした</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>起動</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>14 Route Editer が起動した</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="31" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>後</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>稼働モニタとアンドンの表示を確認した</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-    </row>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40"/>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>13-5 異常・申し送り</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="16" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>発生時刻</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>事象・画面表示</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>中断/対応</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>連絡先</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>記録No.</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="4" t="inlineStr"/>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45" ht="16.5" customHeight="1">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-    </row>
+    <row r="44" ht="17.5" customHeight="1">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45" ht="17.5" customHeight="1">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46"/>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>13-6 承認</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="16" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="17.5" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>承認日</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
+    <row r="50" ht="17.5" customHeight="1">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3153,6 +3255,9 @@
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A47:G47"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3167,9 +3272,9 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -3177,15 +3282,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3198,6 +3305,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3212,485 +3324,487 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>14. 要確認事項一覧(2026-10-05 時点 + 2026-10-13 更新 + 2026-10-14 更新)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>解決した項目は取り消し線で残す。消さない。消すと、同じ調査をやり直すことになる。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="31" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>再起動手順の原本</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-10-13 解決。操作手順書 0494-912039(06)「PanaCIM」シートに異常時再起動14手順を確認し、原文との突合で完全性を立証済み(§10-4 突合表)。月次再起動の記載はシートになし(サーバー再起動.pptx 出典のまま)。※様式の参考は「みるといい」であり絶対ではない(スケジュールリーダ談)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>引用の形式</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>本文へ転記するか、参照先を示すにとどめるか</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>引用元の改訂追従</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>確認する担当者と時期。起案は篠原が担当(第5章)。確認の時期は本会議(10-14)で日程を含め判断する</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>点検の判定基準</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>稼働モニタの正常画面名、バックアップ遡りのしきい値、保存領域のしきい値、アンドンの色定義。判定は実機確認(日程は本会議で決定)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>点検項目の確定</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>第6章の三項目は候補にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>実施時間帯</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>日次点検を実施してよい時間帯、休日の扱い</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>接続先と権限</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>点検に用いる画面名、アカウント、必要な権限。第10章10-4 の手順10と13で使うアカウント</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>異常時の連絡先</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>第10章10-2 の全欄</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>停止の判断者</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>担当は確定済み。氏名の記入が未了。管理責任者の記入待ち(会議記録 §10「本人が担当。後日記入」)。氏名の記入は本会議(10-14)で</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="57" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>復旧</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>実施条件、手順、頻度、記録様式。戻す試験を一度もしていない。現状: 取得できていても戻せるかは未証明。実施条件と頻度の案を持ち寄り済みで、本会議(10-14)で確定する</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="57" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>バックアップ</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>手順は反映済み(第8章)。残るのは保存先の実機確認(E:\BackUP_DB のコロン)、正式な命名規則、外部媒体、保持世代、成否の確認者。確認者の決定は本会議で(§8-2)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="57" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>DGS の位置づけ</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>管理範囲に含めるか、境界の箱として扱うか。現状: 相関図草案(第一層・箱6)でも「要確認(境界候補)」。LNB と DGS の関係の調査・整理は篠原が実施し、判定は本会議(10-14)で。相関図確定の前提</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>記録の管理</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>保存先、保存期間、確認者と確認の時期</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>不具合記録フォーム</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>入力者、入力の契機、権限、ツールと保存先</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>作図の形式</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>ZZZ-90000 へ登録できる図の形式</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>様式の拡張</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>操作の種別、取り消し可否、中断条件の三欄を追加できるか</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>文書番号と保管場所</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>付番規則、保管場所、改訂の承認者</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Windows更新後の扱い</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>更新の翌日に再起動する扱いとするか。判断は本会議(10-14)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="43.5" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>随時再起動</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>第10章10-4 が該当。実施の判断者と、チェックシートへの記入欄の要否。記入欄の可否は本会議(10-14)で判断</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>管理対象の構成</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>サーバの主副と台数、端末の設置場所、バージョン</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>表紙の頁数表記</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>引用元表紙には全47頁と初版枚数48枚の両方の記載がある</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>CIMC-SV の位置づけ</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2026-10-05 解決。VMware 上の仮想マシン(RHEL 6・64ビット)。ESXiホスト 172.25.253.45 上で動く。CIM-A PC・CIM-C PC は物理PC</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="57" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>画像と手順の対応付け</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>image/ に14枚ある。手順3は 画像2.png と確認済み。残り13枚の対応付けが未了。対応付けは実機確認(日程は本会議で決定)。既存xlsx埋込み画像とはMD5不一致(2026-10-13 確認)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Route Editer の表記</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>原文シート(行277)で「Route Editer」の表記を確認済み(2026-10-13)。画面の表示と一致するか要確認</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>公式資料の構成図との対応</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>PanaCIM-EE 外部インターフェース N7201A522J17 の構成図と、本書の管理対象の対応付け</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="84" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>認証情報の保管先</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>本書が参照する「承認済みの保管先」が未確定。第7章・第10章10-4 が参照できない。保管先の決定は本会議(10-14)で。決まるまで第7章・第10章のパスワード欄は運用に使えない。※原文xlsxに平文パスワードが埋め込まれていることが判明(2026-10-13)。新文書へは転記しない</t>
         </is>
@@ -3701,6 +3815,9 @@
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3750,163 +3867,185 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>項目名を選ぶと該当シートへ移動します。各シートの「目次へ」から戻れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>目的と適用範囲</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>用語</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>構成と管理情報</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>管理体制</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>日次点検</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>6.</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>月次再起動</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>バックアップ</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>8.</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>復旧</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>9.</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>異常時の対応</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10.</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>記録と文書管理</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11.</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>チェックシート(日次)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>12.</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>チェックシート(月次・異常時)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>13.</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>要確認事項一覧</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3917,28 +4056,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3951,6 +4092,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3965,310 +4111,338 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>改訂履歴</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>改訂内容</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>初版作成</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>構成と管理情報、チェックシートを追加</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="43.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="31" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>公式資料から再起動手順とバックアップ手順の本文を反映。定期再起動と異常時再起動を別の手順として分離</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>チーム分担(Pana-CIM/LNB=当グループ、Eg-Pro/Asprova=石井G)と背景(要約)を適用範囲に追記。再起動手順の原文突合により完全性を立証(第10章10-4)。目次シートを追加</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="43.5" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>作成の分担を明記(本書と聞き取りは篠原の担当)。未決項目に現状・内容・理由を補記(§8-2)。要確認事項に本会議(10-14)で決める事項を反映</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>LNB側の実機確認結果を反映。Pana-CIM のバックアップは調査段階であることを §8 に明記。LWS・再起動2種・設定情報の自動バックアップ（LNB側）の判明に伴い、DGS 経由のバックアップとの関係を §8 に追記</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>LNB側のキャプチャ解析結果を反映。DGS＝172.25.253.10 が LWS の Pingチェックに「上位システム」として表示される事実を §3 用語に追記。LNB側の再起動ボタンが3種（LNB再起動／LNB-PC電源OFF／LNB-PCリブート）であることに伴い、§8 の記載を補足</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>人名・割り当てを会議記録と再突合。§5 に副管理責任者（倉林筆頭・石井・茂木（絵））の行と「人名と割り当ての対応」を追加。§8-2 に松井さんの持ち帰りタスク（バックアップ取得状況の確認）を紐づけ。§14 No.27 追加。停止判断者の記入待ち先を明記</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>人名・割り当てを本人確認により確定。§5 を改訂（管理責任者＝茂木（由）・倉林の2名体制、副管理責任者＝石井・茂木（絵））。茂木（絵）のスケジュール管理担当を明記。§14 No.27 解決。会議記録 §12 との食い違いは本確定を正とする</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="31" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>版管理の方針を明記（§12）。本書はベータ版（V1未満）であり、正式な版管理は運用開始後に実施する。運用開始（実装）時点で本改訂履歴は削除する予定</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>報告準備。§4-2 に図の読み方（種別ラベル・凡例）と PLM 閲覧問題の現状（大塚さん対応中・解決後に図解を拡充）を追記。構成図に種別ラベルと凡例を導入し視認性を改善</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4278,6 +4452,9 @@
   <mergeCells count="1">
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4292,8 +4469,8 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -4302,15 +4479,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4323,6 +4502,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4337,20 +4521,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>1. 目的</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -4361,21 +4546,23 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2. 適用範囲</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
@@ -4386,8 +4573,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>分担</t>
         </is>
@@ -4398,8 +4585,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -4410,8 +4597,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>未検証</t>
         </is>
@@ -4422,34 +4609,37 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>2-1. 背景(要約)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16" t="n"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>詳細は「LNB・Pana-CIM_管理文書作成_会議記録_追補.md」を参照。本章には経緯の詳細を書かない。</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>経緯</t>
         </is>
@@ -4460,8 +4650,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
@@ -4479,6 +4669,9 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A17:G17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4493,8 +4686,8 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -4503,15 +4696,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4524,6 +4719,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4538,157 +4738,158 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>3. 用語</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>語</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Pana-CIM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>設備から情報を収集するシステム</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="43.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>稼働モニタ</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pana-CIM から出力される表示。会議では「稼働モニタ異常(Power BI)」として言及されており、表示基盤が Power BI であるかは要確認</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>アンドン</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>ラインの状態を表示する装置。異常発生時の対処対象として本書で扱う</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>SMT点検日</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>SMT のラインが稼働しない日。月次再起動の実施日として用いる</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="57" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CIMC-SV</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>VMware 上の仮想マシン。ゲストOSは Red Hat Enterprise Linux 6(64ビット)。ESXiホスト(https://172.25.253.45/ui/)のナビゲータから操作する。ノートPC右隣の白枠モニタに表示される</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>CIM-C PC</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>物理PC。異常時の再起動で最初に止める対象(第10章10-4)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CIM-A PC</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>物理PC。VMware の管理画面へ入るための端末</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ESXi</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>仮想マシンを動かす基盤。ホスト画面から仮想マシンの電源を操作する</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>メンテナンスモード</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ESXi ホストを保守状態にする設定。解除を忘れると仮想マシンを起動できない</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Route Editer</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>異常時の再起動の最後に起動する画面。原文の表記のまま記載している(第10章10-4 手順14)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DGS</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>LNB のバックアップ経路に現れる系。本書での位置づけは要確認</t>
         </is>
@@ -4698,6 +4899,9 @@
   <mergeCells count="1">
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4712,8 +4916,8 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -4722,15 +4926,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4743,6 +4949,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4757,130 +4968,134 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>4. 構成と管理情報 / 4-1 管理対象</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>仮想マシン</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>CIMC-SV(Red Hat Enterprise Linux 6・64ビット)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>仮想化基盤</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ESXi(ホスト画面 https://172.25.253.45/ui/)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>物理PC</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>CIM-C PC、CIM-A PC</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>表示系</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>稼働モニタ、アンドン</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>台数・設置場所</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>バージョン</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>公式資料(PanaCIM-EE 外部インターフェース N7201A522J17)には、PanaCIM アプリケーションサーバー/コントローラーサーバー(ESXi使用)、Webクライアント、LNB(FAパソコン)、NPM-DGS が構成図として示されている。本書の管理対象がこのどれに当たるかの対応付けは要確認(付録A-2)。</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>4-2 相関図</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>粒度の基準</t>
         </is>
@@ -4891,8 +5106,8 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>作成方針</t>
         </is>
@@ -4903,8 +5118,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>作図の形式</t>
         </is>
@@ -4921,6 +5136,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A18:G18"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4935,9 +5153,9 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -4945,15 +5163,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4966,6 +5186,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4980,205 +5205,210 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>5. 管理体制と役割</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>本書の作成と改訂の起案は篠原が担当する(管理文書・手順書・チェックシートの作成、およびそれらを埋めるための聞き取りを含む。2026-10-14 定期報告の「役割の区分」による)。チーム(篠原、大塚、茂木(絵)、竹渕)は進捗の共有と、実機確認の日程・判定事項(担当者・しきい値)の決定で協力する。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>不在時の代行</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>茂木（由）、倉林（2名体制）</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>互いに代行。両者不在時は副管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>副管理責任者</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>石井、茂木（絵）（2名体制）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>管理責任者不在時に代行</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>点検の実施者</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>記録の確認者</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>文書の承認者</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>停止の判断者</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>担当は確定済み。氏名の記入が未了（管理責任者の記入待ち）</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>文書作成</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>篠原、大塚、茂木（絵）、竹渕（リーダー 茂木（絵）・スケジュール管理担当）</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>同チーム内で調整</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>人名と割り当ては 2026-10-14、篠原のグループによる本人確認で確定。会議記録 §12 の「副管理責任者を倉林さんとし」は本確認と食い違うため、本確認を正とする。</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>5-1 作業時の制約</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>大元のパソコンを操作するときは、一人で入らない。付き添う者を確保する。確保できない場合は茂木(由)または倉林に声をかける。この制約は本書のすべての操作に適用する。</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5188,6 +5418,9 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5202,8 +5435,8 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -5212,15 +5445,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5233,6 +5468,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5247,20 +5487,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>6. 日常管理(日次点検)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>周期</t>
         </is>
@@ -5271,8 +5512,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
@@ -5283,249 +5524,256 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>6-1 Step 1 稼働状態を確認する</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="16" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>稼働モニタとアンドンの表示を確認する</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>読み取りのみ</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>表示が出ていること。アンドンの色定義は第10章10-1に従う。稼働モニタ側の「正常と判定する画面名」は要確認</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>記録</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>チェックシートの該当欄に記入する</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>稼働モニタは Pana-CIM から出力されている。表示だけで原因を断定しない</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>6-2 Step 2 バックアップの結果を確認する</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>最終実行日時と成否を確認する</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>読み取りのみ</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="57" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>最終実行日時が記録されており、画面に「データベース完全バックアップに成功しました。」が表示されていること。何日遡ったら異常とするかのしきい値は要確認</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>記録</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>最終実行日時と成否をチェックシートに記入する</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="43.5" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>画面に「4日以上前のバックアップが存在する(DBCleanBackup)」旨が表示される場合がある。表示が出たら確認者へ申し送る</t>
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>6-3 Step 3 保存領域を確認する</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="16" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>空き容量と増加の傾向を確認する</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>読み取りのみ</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>空き容量を数値で読み取り、チェックシートに記入する。注意・異常とみなす値は要確認</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="35"/>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Step 1 から Step 3 はいずれも点検項目の候補であり、確定していない。判定基準は実機の画面を見ながら決める。</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5535,6 +5783,9 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5549,8 +5800,8 @@
   <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -5559,15 +5810,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5580,6 +5833,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5593,243 +5851,253 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6" ht="17.5" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>本章は計画的な月次再起動の手順である。異常が出たときの再起動は手順がまったく異なり、全ラインを停止させる。第10章10-4 を参照すること。取り違えると生産を止める。</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>7-1 実施条件</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>周期</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>月1回</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>SMT点検日の朝</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Pana-CIM が動作していないこと</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>CIMC-SV</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>異常発生時の随時再起動は従来どおり残る。定期と随時の二本立てとなる。Windows 更新後の扱いは要確認(RPA機では更新の翌日に再起動する決まりがあるが、Pana-CIM を同じ扱いとするかは未確定)。</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>7-2 Step 1 Pana-CIM が動いていないことを確認する</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>SMT点検日であること、および Pana-CIM が動作していないことを確認する</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="43.5" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>動作していないと判断できる画面または状態を確認する。判断に用いる画面と、動作中とみなす表示は要確認</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>動作中に再起動すると処理が中断する。中断した場合の影響範囲は要確認</t>
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>7-3 Step 2 付き添う者を確保する</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="16" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>大元のパソコンを操作する前に、同席する者を確保する。確保できない場合は茂木(由)または倉林に声をかける</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>同席者がいる状態で操作を開始する</t>
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>7-4 Step 3 再起動を実施する(操作の種別: 状態を変える)</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="n"/>
-    </row>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="16" t="n"/>
+    </row>
+    <row r="32"/>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>出典は サーバー再起動.pptx(スライド1〜2)。原文は付録A-3。</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="16" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>手順1</t>
         </is>
@@ -5840,8 +6108,8 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>手順2</t>
         </is>
@@ -5852,8 +6120,8 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>手順3</t>
         </is>
@@ -5864,156 +6132,163 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+    <row r="38"/>
+    <row r="39" ht="17.5" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>パスワードは本書に書かない。承認済みの保管先にある値を使う(第12章)。</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="17.5" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="42" ht="17.5" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>取り消し可否</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>要確認。再起動を取り消す方法の有無、中断時の復旧方法</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>ログインが完了し、第6章 Step 1 と同じ表示に戻ること</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="44" ht="17.5" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>操作画面には ESXiホスト画面(https://172.25.253.45/ui/)とナビゲータが表示される</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="45"/>
+    <row r="46" ht="16.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>操作手順書 0494-912039(06) に該当する記載があるかは未確認(第14章 No.1)。→ 2026-10-13 時点で「PanaCIM」シートに異常時再起動の記載を確認済み(月次再起動の記載はなし)。</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="14" t="n"/>
-    </row>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="16" t="n"/>
+    </row>
+    <row r="47"/>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>7-5 Step 4 再起動後の状態を確認する</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="14" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="16" t="n"/>
+    </row>
+    <row r="49"/>
+    <row r="50" ht="17.5" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+    <row r="51" ht="17.5" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>稼働モニタとアンドンの表示を確認する</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+    <row r="52" ht="17.5" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>第6章 Step 1 と同じ状態に戻っていること。判定基準は要確認</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="53" ht="17.5" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>記録</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>チェックシートの月次欄に実施日と実施者を記入する</t>
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>7-6 引用元の改訂への追従</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="14" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="16" t="n"/>
+    </row>
+    <row r="56"/>
+    <row r="57" ht="17.5" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>追従</t>
         </is>
@@ -6038,6 +6313,9 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A46:G46"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
@@ -22,7 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録と文書管理" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(日次)" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(月次・異常時)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会議課題一覧(一時)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'改訂履歴'!$1:$4</definedName>
@@ -38,7 +39,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'記録と文書管理'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'チェックシート(日次)'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'チェックシート(月次・異常時)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'要確認事項一覧'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'会議課題一覧(一時)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'要確認事項一覧'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,11 +109,23 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
       <color rgb="00833C00"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -209,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -241,13 +260,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -848,7 +871,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>周期は毎日とする(2026-09-30 会議の決定)。DGS で取得したものを Pana-CIM で保存する。日次点検の Step 2(第6章)で最終実行日時と成否を確認する。</t>
         </is>
@@ -862,7 +885,7 @@
     </row>
     <row r="9"/>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>出典は 不具合別ログリスト_取得手順_Ｊ.pdf(PDF通し11〜12頁)。原文は付録A-1。</t>
         </is>
@@ -876,7 +899,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>手順1</t>
         </is>
@@ -888,7 +911,7 @@
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>手順2</t>
         </is>
@@ -900,7 +923,7 @@
       </c>
     </row>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>手順3</t>
         </is>
@@ -912,7 +935,7 @@
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>手順4</t>
         </is>
@@ -924,7 +947,7 @@
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>手順5</t>
         </is>
@@ -936,7 +959,7 @@
       </c>
     </row>
     <row r="17" ht="17.5" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>手順6</t>
         </is>
@@ -949,7 +972,7 @@
     </row>
     <row r="18"/>
     <row r="19" ht="17.5" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>保存先の表記について。原文のPDFから抽出した文字列は E\BackUP_DB で、ドライブ文字の後のコロンが落ちている。本書では E:\BackUP_DB と書いた。実機の画面で正しい保存先を確認すること(第14章 No.11)。</t>
         </is>
@@ -977,12 +1000,12 @@
     </row>
     <row r="22"/>
     <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
@@ -1050,7 +1073,7 @@
     </row>
     <row r="29"/>
     <row r="30" ht="17.5" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>バックアップ障害は「成否を確認する担当が決まっていなかった」ことで長期化している。Eg-Pro のサブサーバー同期は1年以上、nksv523 は6月から暫定運用のまま。手順書を作るだけでは同じことが起きる。誰がどこで結果を確認し、失敗時に何をするかまで決める。</t>
         </is>
@@ -1154,7 +1177,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
@@ -1166,7 +1189,7 @@
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>実施条件</t>
         </is>
@@ -1178,7 +1201,7 @@
       </c>
     </row>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
@@ -1190,7 +1213,7 @@
       </c>
     </row>
     <row r="11" ht="17.5" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>確認の頻度</t>
         </is>
@@ -1202,7 +1225,7 @@
       </c>
     </row>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>記録様式</t>
         </is>
@@ -1215,7 +1238,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>戻す試験を一度もしていない。本書の初版では復旧手順を確定できていない。</t>
         </is>
@@ -1315,7 +1338,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
@@ -1327,7 +1350,7 @@
       </c>
     </row>
     <row r="9" ht="44.5" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>記載する事象</t>
         </is>
@@ -1339,7 +1362,7 @@
       </c>
     </row>
     <row r="10" ht="44.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>稼働モニタ</t>
         </is>
@@ -1351,7 +1374,7 @@
       </c>
     </row>
     <row r="11" ht="17.5" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>色定義の表</t>
         </is>
@@ -1378,7 +1401,7 @@
     </row>
     <row r="14"/>
     <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -1390,7 +1413,7 @@
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>最初の連絡先</t>
         </is>
@@ -1402,7 +1425,7 @@
       </c>
     </row>
     <row r="17" ht="31" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>連絡がつかない場合</t>
         </is>
@@ -1414,7 +1437,7 @@
       </c>
     </row>
     <row r="18" ht="31" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>その場で行ってよい対応</t>
         </is>
@@ -1426,7 +1449,7 @@
       </c>
     </row>
     <row r="19" ht="31" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>行ってはいけない対応</t>
         </is>
@@ -1438,7 +1461,7 @@
       </c>
     </row>
     <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>中断して連絡する条件</t>
         </is>
@@ -1451,7 +1474,7 @@
     </row>
     <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>バックアップ失敗、保存領域不足、通信異常は記録番号を付して申し送る。復旧操作とサーバ構成の変更は本手順の範囲外。ベンダーへの依頼境界は要確認。</t>
         </is>
@@ -1479,7 +1502,7 @@
     </row>
     <row r="25"/>
     <row r="26" ht="31" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>媒体</t>
         </is>
@@ -1491,7 +1514,7 @@
       </c>
     </row>
     <row r="27" ht="31" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>事例</t>
         </is>
@@ -1503,7 +1526,7 @@
       </c>
     </row>
     <row r="28" ht="31" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
@@ -1530,7 +1553,7 @@
     </row>
     <row r="31"/>
     <row r="32" ht="17.5" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>本手順は全ラインの生産と作業を停止させる。第7章の月次再起動とはまったく別の手順である。実施には停止判断者の承認が要る。</t>
         </is>
@@ -1544,7 +1567,7 @@
     </row>
     <row r="33"/>
     <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>発動条件(原文): 生産時、「生産情報が取得できません。」とエラーが発生し情報の取得ができない場合、以下の手順で PanaCIM サーバーの再起動を実施してください。</t>
         </is>
@@ -1558,7 +1581,7 @@
     </row>
     <row r="35"/>
     <row r="36" ht="31" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
@@ -1570,7 +1593,7 @@
       </c>
     </row>
     <row r="37" ht="44.5" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>構成</t>
         </is>
@@ -1597,17 +1620,17 @@
     </row>
     <row r="40"/>
     <row r="41" ht="17.5" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>原文の位置</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>突合結果</t>
         </is>
@@ -1717,7 +1740,7 @@
     </row>
     <row r="48"/>
     <row r="49" ht="17.5" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>結論: 手順内容は原文から変化していない。差分は3点(パスワード伏字/綴り訂正/2段構成)で、いずれも意図的かつ注記済みである。</t>
         </is>
@@ -1745,17 +1768,17 @@
     </row>
     <row r="52"/>
     <row r="53" ht="17.5" customHeight="1">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -1879,17 +1902,17 @@
     </row>
     <row r="62"/>
     <row r="63" ht="17.5" customHeight="1">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
@@ -2025,7 +2048,7 @@
     </row>
     <row r="72"/>
     <row r="73" ht="17.5" customHeight="1">
-      <c r="A73" s="19" t="inlineStr">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>パスワードは本書に書かない。手順2、8、10、13 で必要になる値は、承認済みの保管先を参照する(第12章)。</t>
         </is>
@@ -2039,12 +2062,12 @@
     </row>
     <row r="74"/>
     <row r="75" ht="17.5" customHeight="1">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
@@ -2196,12 +2219,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
@@ -2271,12 +2294,12 @@
     </row>
     <row r="15"/>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
@@ -2442,7 +2465,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>対象システム</t>
         </is>
@@ -2454,7 +2477,7 @@
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>年月</t>
         </is>
@@ -2466,7 +2489,7 @@
       </c>
     </row>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
@@ -2479,7 +2502,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>空欄のまま提出しない。実施しなかった項目は「未実施」または「該当なし」と書く。空欄は「実施したが記入を忘れた」と区別できない。状態を変える操作は、同席者と権限者の判断を記録する。</t>
         </is>
@@ -2493,37 +2516,37 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>稼働モニタ/アンドン</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>バックアップ日時・成否</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>空き容量</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>異常記録No.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
@@ -2584,7 +2607,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="85" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>稼働状態</t>
         </is>
@@ -2596,7 +2619,7 @@
       </c>
     </row>
     <row r="22" ht="125.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>バックアップ結果</t>
         </is>
@@ -2608,7 +2631,7 @@
       </c>
     </row>
     <row r="23" ht="31" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>保存領域</t>
         </is>
@@ -2620,7 +2643,7 @@
       </c>
     </row>
     <row r="24" ht="44.5" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
@@ -2720,37 +2743,37 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>保存先</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>成功表示</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>ファイル名</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>媒体退避・圧縮</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
@@ -2790,27 +2813,27 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -2884,7 +2907,7 @@
     </row>
     <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>随時再起動の記入欄を設けるかは未確定のため、本様式には設けていない。</t>
         </is>
@@ -2912,7 +2935,7 @@
     </row>
     <row r="25"/>
     <row r="26" ht="17.5" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>全ラインを停止させる手順。実施前に停止判断者の承認を記録する。</t>
         </is>
@@ -2926,32 +2949,32 @@
     </row>
     <row r="27"/>
     <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>段</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>実施時刻</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -3149,32 +3172,32 @@
     </row>
     <row r="42"/>
     <row r="43" ht="17.5" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>発生時刻</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>事象・画面表示</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>中断/対応</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>連絡先</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>記録No.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
@@ -3212,27 +3235,27 @@
     </row>
     <row r="48"/>
     <row r="49" ht="17.5" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>承認日</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -3269,6 +3292,742 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>手 順 書</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>型   名</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ZZZ-90000(仮)</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>作業内容</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>会議課題一覧(一時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>会議で上がった課題の一覧(一時掲載)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>本シートは会議の場での一覧性を確保するための一時掲載。正本は各管理書(md)の該当章であり、解決後は正本側を更新する。達成度の目安: 反映済み=文書に入った(実機確認や決定が残る)/草案あり=持ち寄り案・骨格まで作成済み(会議の判断で確定)/着手=一部作成/未着手・未決=作業または決定がまだ。</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>A. 9-30 会議で挙がった課題12件の達成度</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>達成度</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>現状と残務</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>月次再起動手順</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>管理書 §7 に実手順ベースで記載(SMT点検日の朝・Pana-CIM停止確認)。チェックシートに月次必須項目あり。残務: LNB 側は月次作業の有無自体が未確認(LNB管理書 §14 No.27)。確認方法: 篠原が現行実施者に聞き取り</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>draw.io 相関図 第一層</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>草案あり</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>会議要件どおりの作り直し案を完成(箱6+境界2・線4本)。既存 drawio は業務フロー図のため第一層には使わない。残務: 会議で DGS の位置づけと各箱の管理担当を確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>バックアップ(周期・保存)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>管理書 §8 に「周期は毎日・DGSで取得し Pana-CIM で保存」を明記。日次点検 Step 2 で成否確認。残務: 成否の確認者が未決(§8 で最も重要)。戻す試験は未実施(⑫)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>トラブルシューティング</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>管理書 §10-1 に事象2件(アンドン異常/稼働モニタ異常(Power BI))→再起動手順、正常画面(TrueCase)併記の方針を追記。残務: 画像14枚のうち13枚の対応付け、色定義、記録フォームの所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>チェックシートの有無</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>草案あり</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>「あり」で確定(管理手順書に内包)。三項目(稼働状態/バックアップ結果/保存領域)の判定基準案を作成済み。残務: しきい値を実機画面で決定。記録の確認者</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LNB の点検項目</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LNB管理書 §6 は枠のみ。公式資料に書かれた「LNB接続状態」を聞き取りの出発点として Step 1 に準備済み。項目名すら定まっていない(会議記録 §7)。聞き取りは篠原が実施。本会議で日程を決めること(ネック)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>バックアップのデータ確認(誰が・いつ・どこに)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L1/L2/L3 それぞれで取得していることは会議で確認済み(会議記録 §5)。各ラインで誰が・いつ・どこに保存しているかが必要。確認の材料として LNB_Collector による現場収集(§5)を準備済み。確認先の候補挙げは篠原が実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44.5" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LNB と DGS の中身の確認・関連性整理</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DGS は管理書 §3 用語で「位置づけは要確認」のまま。相関図草案(箱6)でも DGS の管理範囲は「要確認(境界候補)」。調査・整理は篠原が実施し、判定は本会議で。相関図②確定の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44.5" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>異常時の連絡先と停止判断者</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>未決</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>役割の行は管理書 §5/LNB管理書 §5 にあり、停止判断者の担当は確定済みだが氏名が空欄。管理責任者の記入待ち(会議記録 §10「本人が担当。後日記入」)。文書側の受け皿は完成済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>管理手順書の草案作成</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pana-CIM v0.11(骨格完成)/LNB v0.9(骨格のみ)。残務: v0.5 相当(基準反映版)は11月中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>認証情報の保管先</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>未決</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LNB 接続 URL 3件に利用者名とパスワードが平文で埋め込まれていることを確認(LNB管理書 §15)。本文に書かない方針は確定済みだが、書かない前提の「安全な保管先」が存在しないため、§4-2・§15 の参照先が決められない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>⑫</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>復旧(戻す試験)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>管理書 §9 は実施条件・頻度とも要確認のまま。取得できていても戻せるかは別であり(管理書 §9)、試験をしないとバックアップの有効性が未証明。実施条件と頻度の案を持ち寄り済み。本会議で確定すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>B. 10-14 会議(13:10)で決定を求める9点</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>内容と背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>実機確認の日程</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>最優先。しきい値(正常画面名・色定義・遡り日数・容量)、画像13枚の対応付け、バックアップ保存先の実物確認を1回の訪問で済ませたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LNB 聞き取りの担当と日程</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>最優先。全体のネック。ここが進まないと LNB 管理書は空白のままで、12月の登録に間に合わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>バックアップ成否の確認者</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>管理書 §8 で最も重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>異常時の連絡先と停止判断者の氏名記入</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>文書側の受け皿は完成済み。管理責任者の記入待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>認証情報の保管先</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>保管先を決めれば文書側は記載できる。現状は LNB 接続 URL に平文埋め込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>復旧(戻す試験)の実施条件と頻度</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>案を持ち寄り済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Windows 更新後の扱い</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RPA 機と同じ「更新の翌日に再起動」にするか</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>随時再起動の記入欄の可否</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>チェックシートへの記入欄を追加できるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LNB と DGS の中身確認の担当</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>持ち帰りタスクで未定になっている分。相関図確定の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>C. 解決済みの項目(取り消し線で残す運用の掲載分)</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="17.5" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>書</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>解決日と内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>CIMC-SV の位置づけ</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-05 解決。VMware 上の仮想マシン(RHEL 6・64ビット)。ESXiホスト 172.25.253.45 上で動く。CIM-A PC・CIM-C PC は物理PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44.5" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>No.1(一部)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>再起動手順の原本</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 解決。操作手順書 0494-912039(06)「PanaCIM」シートに異常時再起動14手順を確認し、原文との突合で完全性を立証済み(管理書 §10-4 突合表)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>人名・割り当ての確認</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。管理責任者＝茂木（由）・倉林、副管理責任者＝石井・茂木（絵）と確定(本人確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44.5" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>稼働率フォルダの中身の確認</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。稼働率フォルダにはラインごとの稼働率データ(Pana-CIM 出力の HTML・20260814-1L.htm)が保存されていることを実物で確認。大塚さんへの確認依頼は取り下げ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>人名・割り当ての確認</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。Pana-CIM 側 No.27 と同じ内容(§5)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3338,7 +4097,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>解決した項目は取り消し線で残す。消さない。消すと、同じ調査をやり直すことになる。</t>
         </is>
@@ -3352,34 +4111,34 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>再起動手順の原本</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>2026-10-13 解決。操作手順書 0494-912039(06)「PanaCIM」シートに異常時再起動14手順を確認し、原文との突合で完全性を立証済み(§10-4 突合表)。月次再起動の記載はシートになし(サーバー再起動.pptx 出典のまま)。※様式の参考は「みるといい」であり絶対ではない(スケジュールリーダ談)</t>
         </is>
@@ -3726,17 +4485,17 @@
       </c>
     </row>
     <row r="32" ht="17.5" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>CIMC-SV の位置づけ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>2026-10-05 解決。VMware 上の仮想マシン(RHEL 6・64ビット)。ESXiホスト 172.25.253.45 上で動く。CIM-A PC・CIM-C PC は物理PC</t>
         </is>
@@ -3829,7 +4588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4025,6 +4784,18 @@
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>会議課題一覧(一時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>14.</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>要確認事項一覧</t>
         </is>
@@ -4045,6 +4816,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4125,27 +4897,27 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>改訂内容</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
@@ -4368,27 +5140,27 @@
       </c>
     </row>
     <row r="17" ht="44.5" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>人名・割り当てを本人確認により確定。§5 を改訂（管理責任者＝茂木（由）・倉林の2名体制、副管理責任者＝石井・茂木（絵））。茂木（絵）のスケジュール管理担当を明記。§14 No.27 解決。会議記録 §12 との食い違いは本確定を正とする</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4422,27 +5194,27 @@
       </c>
     </row>
     <row r="19" ht="31" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>報告準備。§4-2 に図の読み方（種別ラベル・凡例）と PLM 閲覧問題の現状（大塚さん対応中・解決後に図解を拡充）を追記。構成図に種別ラベルと凡例を導入し視認性を改善</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4535,7 +5307,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -4562,7 +5334,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
@@ -4574,7 +5346,7 @@
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>分担</t>
         </is>
@@ -4586,7 +5358,7 @@
       </c>
     </row>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -4598,7 +5370,7 @@
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>未検証</t>
         </is>
@@ -4625,7 +5397,7 @@
     </row>
     <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>詳細は「LNB・Pana-CIM_管理文書作成_会議記録_追補.md」を参照。本章には経緯の詳細を書かない。</t>
         </is>
@@ -4639,7 +5411,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="17.5" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>経緯</t>
         </is>
@@ -4651,7 +5423,7 @@
       </c>
     </row>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
@@ -4752,12 +5524,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>語</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
@@ -4982,12 +5754,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5067,7 +5839,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>公式資料(PanaCIM-EE 外部インターフェース N7201A522J17)には、PanaCIM アプリケーションサーバー/コントローラーサーバー(ESXi使用)、Webクライアント、LNB(FAパソコン)、NPM-DGS が構成図として示されている。本書の管理対象がこのどれに当たるかの対応付けは要確認(付録A-2)。</t>
         </is>
@@ -5095,7 +5867,7 @@
     </row>
     <row r="19"/>
     <row r="20" ht="17.5" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>粒度の基準</t>
         </is>
@@ -5107,7 +5879,7 @@
       </c>
     </row>
     <row r="21" ht="17.5" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>作成方針</t>
         </is>
@@ -5119,7 +5891,7 @@
       </c>
     </row>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>作図の形式</t>
         </is>
@@ -5219,7 +5991,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>本書の作成と改訂の起案は篠原が担当する(管理文書・手順書・チェックシートの作成、およびそれらを埋めるための聞き取りを含む。2026-10-14 定期報告の「役割の区分」による)。チーム(篠原、大塚、茂木(絵)、竹渕)は進捗の共有と、実機確認の日程・判定事項(担当者・しきい値)の決定で協力する。</t>
         </is>
@@ -5233,17 +6005,17 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>不在時の代行</t>
         </is>
@@ -5370,7 +6142,7 @@
     </row>
     <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>人名と割り当ては 2026-10-14、篠原のグループによる本人確認で確定。会議記録 §12 の「副管理責任者を倉林さんとし」は本確認と食い違うため、本確認を正とする。</t>
         </is>
@@ -5398,7 +6170,7 @@
     </row>
     <row r="22"/>
     <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>大元のパソコンを操作するときは、一人で入らない。付き添う者を確保する。確保できない場合は茂木(由)または倉林に声をかける。この制約は本書のすべての操作に適用する。</t>
         </is>
@@ -5501,7 +6273,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>周期</t>
         </is>
@@ -5513,7 +6285,7 @@
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
@@ -5540,12 +6312,12 @@
     </row>
     <row r="12"/>
     <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5627,12 +6399,12 @@
     </row>
     <row r="21"/>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5714,12 +6486,12 @@
     </row>
     <row r="30"/>
     <row r="31" ht="17.5" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5763,7 +6535,7 @@
     </row>
     <row r="35"/>
     <row r="36" ht="17.5" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Step 1 から Step 3 はいずれも点検項目の候補であり、確定していない。判定基準は実機の画面を見ながら決める。</t>
         </is>
@@ -5852,7 +6624,7 @@
       </c>
     </row>
     <row r="6" ht="17.5" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>本章は計画的な月次再起動の手順である。異常が出たときの再起動は手順がまったく異なり、全ラインを停止させる。第10章10-4 を参照すること。取り違えると生産を止める。</t>
         </is>
@@ -5880,12 +6652,12 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5941,7 +6713,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>異常発生時の随時再起動は従来どおり残る。定期と随時の二本立てとなる。Windows 更新後の扱いは要確認(RPA機では更新の翌日に再起動する決まりがあるが、Pana-CIM を同じ扱いとするかは未確定)。</t>
         </is>
@@ -5969,12 +6741,12 @@
     </row>
     <row r="19"/>
     <row r="20" ht="17.5" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -6032,12 +6804,12 @@
     </row>
     <row r="26"/>
     <row r="27" ht="17.5" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -6083,7 +6855,7 @@
     </row>
     <row r="32"/>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>出典は サーバー再起動.pptx(スライド1〜2)。原文は付録A-3。</t>
         </is>
@@ -6097,7 +6869,7 @@
     </row>
     <row r="34"/>
     <row r="35" ht="17.5" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>手順1</t>
         </is>
@@ -6109,7 +6881,7 @@
       </c>
     </row>
     <row r="36" ht="17.5" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>手順2</t>
         </is>
@@ -6121,7 +6893,7 @@
       </c>
     </row>
     <row r="37" ht="17.5" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>手順3</t>
         </is>
@@ -6134,7 +6906,7 @@
     </row>
     <row r="38"/>
     <row r="39" ht="17.5" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>パスワードは本書に書かない。承認済みの保管先にある値を使う(第12章)。</t>
         </is>
@@ -6148,12 +6920,12 @@
     </row>
     <row r="40"/>
     <row r="41" ht="17.5" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -6197,7 +6969,7 @@
     </row>
     <row r="45"/>
     <row r="46" ht="16.5" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>操作手順書 0494-912039(06) に該当する記載があるかは未確認(第14章 No.1)。→ 2026-10-13 時点で「PanaCIM」シートに異常時再起動の記載を確認済み(月次再起動の記載はなし)。</t>
         </is>
@@ -6225,12 +6997,12 @@
     </row>
     <row r="49"/>
     <row r="50" ht="17.5" customHeight="1">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -6288,7 +7060,7 @@
     </row>
     <row r="56"/>
     <row r="57" ht="17.5" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>追従</t>
         </is>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
@@ -23,7 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(日次)" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(月次・異常時)" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会議課題一覧(一時)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="付録 引用元と確認範囲" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'改訂履歴'!$1:$4</definedName>
@@ -40,7 +41,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'チェックシート(日次)'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'チェックシート(月次・異常時)'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'会議課題一覧(一時)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'要確認事項一覧'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'付録 引用元と確認範囲'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'要確認事項一覧'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2674,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2779,7 +2781,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="17.5" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
@@ -2788,7 +2790,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
-    <row r="10" ht="17.5" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
@@ -3203,7 +3205,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="17.5" customHeight="1">
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
@@ -3211,7 +3213,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
     </row>
-    <row r="45" ht="17.5" customHeight="1">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
@@ -3219,64 +3221,72 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
     </row>
-    <row r="46"/>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>13-6 承認</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="16" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49" ht="17.5" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="16" t="n"/>
+    </row>
+    <row r="49"/>
+    <row r="50" ht="17.5" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>承認日</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="17.5" customHeight="1">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
@@ -4028,6 +4038,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>手 順 書</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>型   名</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ZZZ-90000(仮)</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>作業内容</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>付録 引用元と確認範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>付録A 引用元の原文</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>改変せずに載せる。本文は読みやすさのために整えてあるので、食い違いがあれば本付録を正とする。原文の認証情報は伏字にした。操作時は承認済みの保管先を参照する(§14 No.26)。文書番号と該当ページは資料管理台帳との照合が未確認。</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>A-1 バックアップ(不具合別ログリスト_取得手順_Ｊ.pdf・PDF通し11〜12頁)</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>原文</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1 PanaCIM コンソールを起動します。2 「データベースユーティリティ」→「バックアップ」→「バックアップ設定」→「バックアップ実行」のタグを選択します。3 「データベースバックアップ場所」を確認します。例）E\BackUP_DB 確認後、「実行開始」をクリックします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>原文(続き)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>4 バックアップの保存が完了後、「データベース完全バックアップに成功しました。」が表示されます。5 データベースバックアップの場所を開きます。例）E\BackUP_DB 6 画面下の方に「PANACIM_****.**.**_**.**.**_FULbak」のファイルがあります。そのファイルを USB、SD カードなどにコピーします。コピー後、ファイルサイズが大きいため、圧縮して下さい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>抽出時の注記</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>E\BackUP_DB はコロンが落ちている。FULbak の前の ****.**.** は日付と時刻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>A-2 システム構成(PanaCIM-EE 外部インターフェース N7201A522J17・PDF通し11〜12頁)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>原文</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>PanaCIM を利用したシステム構成として、PanaCIM アプリケーションサーバー／コントローラーサーバー（ESXi使用）、Webクライアント、LNB（FAパソコン）、NPM-DGS 等が図示されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>A-3 月次再起動(サーバー再起動.pptx・スライド1〜2)</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>原文</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>①通常の Windows と同様に、スタート→再起動を選択してください。②理由コードを聞かれるので、その他（計画外）を選択してください。③ログイン画面が起動したら、下記パスワードを入力してログインしてください。［認証情報は安全上、伏字］</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>A-4 異常時のサーバー再起動(操作手順書)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="98.5" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>原文</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>■生産時、「生産情報が取得できません。」とエラーが発生し情報の取得ができない場合、以下の手順でPanaCIMサーバーの再起動を実施してください。1. 全ラインの生産と作業を停止させる。2. 「CIM-C」画面に移動し、①→②→③の順に選択する。シャットダウン時、パスワードを要求されるため「［認証情報：伏字］」と入力する。3. 停止後、ペンギンの写真が出てくるので、出てきたら「CIM-C」の画面を閉じる。4. ホスト→アクション→メンテナンスモードを選択する。※この時、「メンテナンスモードへ変更しますか？」とポップアップが表示されるため、「はい」を選択する。5. ①→②の順で選択する。初期画面が表示されたら×で閉じる。6. CIM-A PCはwindwosボタン選択後、シャットダウンを選択する。7. CIM-C PCとCIM-A PCの電源を立ち上げる。電源立ち上げ後は約3分待つ。8. モニターにCIM-A PCの情報が表示されるのでログオンする。パスワード「［認証情報：伏字］」サーバーマネージャーが起動しているので閉じてください。9. FirefoxアイコンをクリックしVMWareアイコンをクリックする。10. ユーザー名、パスワードを入力し、ログオンボタンを選択する。11. ホスト→アクション→メンテナンスモードの終了を選択する。12. CIMC-SV→アクション→パワーオンを選択する。13. 画像部分をクリックし拡大させ、ユーザーとパスワードを入力する。※立上げ途中に以下の画面が表示された場合は、「Continue」をクリックしてください。14. 画面が起動するので「Route Editer」を選択して立上げ完了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>本文との差分</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>第10章10-4 への反映時に、停止と起動の2段に分けた。windwos を Windows と直した。それ以外は原文のとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>付録B 資料の確認範囲</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="16" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>確認したもの</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>統合前の管理手順書、点検手順、チェックリスト、および関連資料。PDF 11冊は本文抽出とキーワード確認を済ませた。操作に直接反映した引用は付録Aのとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>原則</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>その他のPDFに新しい事実があった場合は、適用の確認を経てから反映する。推測で手順化しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>確認できていないもの</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>PDF資料の不足2件 / 再起動手順の原本番号 / 資料管理台帳との照合（文書番号・該当ページ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>保持する前提</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>実機未検証 / 認証情報は別紙管理 / 未確定事項は「要確認」として残す</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4588,7 +4910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4796,6 +5118,18 @@
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>付録 引用元と確認範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>15.</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>要確認事項一覧</t>
         </is>
@@ -4817,6 +5151,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/PanaCIM管理手順書_草案.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0.11(草案・未検証)</t>
+          <t>0.12(草案・未検証)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>出典は 不具合別ログリスト_取得手順_Ｊ.pdf(PDF通し11〜12頁)。原文は付録A-1。</t>
+          <t>2026-10-14 会議で確認された現状: DGS 側でバックアップを実施中。実行は端末ごとの手作業であり、実施時間は端末によってまちまち。Pana-CIM 側で一括・自動化できないかを調査中(第14章 No.11)。</t>
         </is>
       </c>
       <c r="B10" s="15" t="n"/>
@@ -900,97 +900,97 @@
       <c r="G10" s="16" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>手順1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>PanaCIM コンソールを起動する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>手順2</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>「データベースユーティリティ」→「バックアップ」→「バックアップ設定」→「バックアップ実行」のタブを選択する</t>
-        </is>
-      </c>
-    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>出典は 不具合別ログリスト_取得手順_Ｊ.pdf(PDF通し11〜12頁)。原文は付録A-1。</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>手順3</t>
+          <t>手順1</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>「データベースバックアップ場所」を確認する(例 E:\BackUP_DB)。確認後、「実行開始」をクリックする</t>
+          <t>PanaCIM コンソールを起動する</t>
         </is>
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>手順4</t>
+          <t>手順2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>保存が完了すると「データベース完全バックアップに成功しました。」が表示される</t>
+          <t>「データベースユーティリティ」→「バックアップ」→「バックアップ設定」→「バックアップ実行」のタブを選択する</t>
         </is>
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>手順5</t>
+          <t>手順3</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>バックアップの場所(例 E:\BackUP_DB)を開く</t>
+          <t>「データベースバックアップ場所」を確認する(例 E:\BackUP_DB)。確認後、「実行開始」をクリックする</t>
         </is>
       </c>
     </row>
     <row r="17" ht="17.5" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
+          <t>手順4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>保存が完了すると「データベース完全バックアップに成功しました。」が表示される</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>手順5</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>バックアップの場所(例 E:\BackUP_DB)を開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>手順6</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>画面下に PANACIM_&lt;日付&gt;_&lt;時刻&gt;_FULbak のファイルがある。USB や SD カードへコピーする。ファイルサイズが大きいため、コピー後に圧縮する</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="17.5" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+    <row r="20"/>
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>保存先の表記について。原文のPDFから抽出した文字列は E\BackUP_DB で、ドライブ文字の後のコロンが落ちている。本書では E:\BackUP_DB と書いた。実機の画面で正しい保存先を確認すること(第14章 No.11)。</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="16" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>8-2 確定していないこと</t>
         </is>
       </c>
       <c r="B21" s="15" t="n"/>
@@ -1001,100 +1001,115 @@
       <c r="G21" s="16" t="n"/>
     </row>
     <row r="22"/>
-    <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>8-2 確定していないこと</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17.5" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ファイル名の正式な命名規則</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>要確認。原文の ****.**.** は抽出時の伏字</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="17.5" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>外部媒体の種類と管理</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>要確認</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17.5" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>保持する世代数と期間</t>
+          <t>ファイル名の正式な命名規則</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>要確認。原文の ****.**.** は抽出時の伏字</t>
         </is>
       </c>
     </row>
     <row r="27" ht="17.5" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
+          <t>外部媒体の種類と管理</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>保持する世代数と期間</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>取得者と取得時刻</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="31" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="30" ht="31" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>成否を確認する担当者</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>要確認。本節で最も重要。現状: L1/L2/L3 それぞれで取得していることは会議で確認済みだが、誰が・いつ・どこに保存しているかは未確認。確認先の候補挙げは篠原が実施し(会議記録 §10 持ち帰りタスク)、実施者の確定は本会議(10-14)で判断する</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30" ht="17.5" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>バックアップ障害は「成否を確認する担当が決まっていなかった」ことで長期化している。Eg-Pro のサブサーバー同期は1年以上、nksv523 は6月から暫定運用のまま。手順書を作るだけでは同じことが起きる。誰がどこで結果を確認し、失敗時に何をするかまで決める。</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="16" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
@@ -5163,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5550,6 +5565,33 @@
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第2回会議(10-14 13:10)の結果を反映。§8 にバックアップの現状（DGS側で実施中・端末ごとの手作業・実施時間はまちまち・Pana-CIM 側一括化を調査中）を追記</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>未</t>
         </is>
